--- a/Reporte_gastos/tabla_gastos_zonas_2026-1.xlsx
+++ b/Reporte_gastos/tabla_gastos_zonas_2026-1.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="21">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="24">
   <si>
     <t xml:space="preserve">TIENDA</t>
   </si>
@@ -21,6 +21,15 @@
   </si>
   <si>
     <t xml:space="preserve">Sueldos</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Incentivo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Contribuciones</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Total_sueldos</t>
   </si>
   <si>
     <t xml:space="preserve">Alquileres</t>
@@ -425,326 +434,461 @@
       <c r="G1" t="s">
         <v>6</v>
       </c>
+      <c r="H1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" t="s">
+        <v>9</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="B2" t="n">
         <v>49769692.16</v>
       </c>
       <c r="C2" t="n">
+        <v>3540084.06183072</v>
+      </c>
+      <c r="D2" t="n">
+        <v>78358</v>
+      </c>
+      <c r="E2" t="n">
+        <v>1106086.46324708</v>
+      </c>
+      <c r="F2" t="n">
         <v>4724528.5250778</v>
       </c>
-      <c r="D2" t="n">
+      <c r="G2" t="n">
         <v>7525000</v>
       </c>
-      <c r="E2" t="n">
+      <c r="H2" t="n">
         <v>482850.5</v>
       </c>
-      <c r="F2" t="n">
+      <c r="I2" t="n">
         <v>8007850.5</v>
       </c>
-      <c r="G2" t="n">
+      <c r="J2" t="n">
         <v>1912542.8</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="B3" t="n">
         <v>25475593.41</v>
       </c>
       <c r="C3" t="n">
+        <v>2459481.47649547</v>
+      </c>
+      <c r="D3" t="n">
+        <v>120536</v>
+      </c>
+      <c r="E3" t="n">
+        <v>787038.230649752</v>
+      </c>
+      <c r="F3" t="n">
         <v>3367055.70714522</v>
       </c>
-      <c r="D3" t="n">
+      <c r="G3" t="n">
         <v>2451875.16</v>
       </c>
-      <c r="E3" t="n">
+      <c r="H3" t="n">
         <v>2223483.52</v>
       </c>
-      <c r="F3" t="n">
+      <c r="I3" t="n">
         <v>4675358.68</v>
       </c>
-      <c r="G3" t="n">
+      <c r="J3" t="n">
         <v>339520.31</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="B4" t="n">
         <v>75245285.57</v>
       </c>
       <c r="C4" t="n">
+        <v>5999565.53832619</v>
+      </c>
+      <c r="D4" t="n">
+        <v>198894</v>
+      </c>
+      <c r="E4" t="n">
+        <v>1893124.69389683</v>
+      </c>
+      <c r="F4" t="n">
         <v>8091584.23222301</v>
       </c>
-      <c r="D4" t="n">
+      <c r="G4" t="n">
         <v>9976875.16</v>
       </c>
-      <c r="E4" t="n">
+      <c r="H4" t="n">
         <v>2706334.02</v>
       </c>
-      <c r="F4" t="n">
+      <c r="I4" t="n">
         <v>12683209.18</v>
       </c>
-      <c r="G4" t="n">
+      <c r="J4" t="n">
         <v>2252063.11</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="B5" t="n">
         <v>39662999.96</v>
       </c>
       <c r="C5" t="n">
+        <v>2736568.87513761</v>
+      </c>
+      <c r="D5" t="n">
+        <v>163806</v>
+      </c>
+      <c r="E5" t="n">
+        <v>888752.933586789</v>
+      </c>
+      <c r="F5" t="n">
         <v>3789127.8087244</v>
       </c>
-      <c r="D5" t="n">
+      <c r="G5" t="n">
         <v>3323410.48</v>
       </c>
-      <c r="E5" t="n">
+      <c r="H5" t="n">
         <v>576451.13</v>
       </c>
-      <c r="F5" t="n">
+      <c r="I5" t="n">
         <v>3899861.61</v>
       </c>
-      <c r="G5" t="n">
+      <c r="J5" t="n">
         <v>2698204.61</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="B6" t="n">
         <v>21769881.93</v>
       </c>
       <c r="C6" t="n">
+        <v>2060419.85</v>
+      </c>
+      <c r="D6" t="n">
+        <v>105530</v>
+      </c>
+      <c r="E6" t="n">
+        <v>655171.13036</v>
+      </c>
+      <c r="F6" t="n">
         <v>2821120.98036</v>
       </c>
-      <c r="D6" t="n">
+      <c r="G6" t="n">
         <v>850000</v>
       </c>
-      <c r="E6" t="n">
+      <c r="H6" t="n">
         <v>279156.28</v>
       </c>
-      <c r="F6" t="n">
+      <c r="I6" t="n">
         <v>1129156.28</v>
       </c>
-      <c r="G6" t="n">
+      <c r="J6" t="n">
         <v>580917.63</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="B7" t="n">
         <v>61432881.89</v>
       </c>
       <c r="C7" t="n">
+        <v>4796988.72513761</v>
+      </c>
+      <c r="D7" t="n">
+        <v>269336</v>
+      </c>
+      <c r="E7" t="n">
+        <v>1543924.06394679</v>
+      </c>
+      <c r="F7" t="n">
         <v>6610248.7890844</v>
       </c>
-      <c r="D7" t="n">
+      <c r="G7" t="n">
         <v>4173410.48</v>
       </c>
-      <c r="E7" t="n">
+      <c r="H7" t="n">
         <v>855607.41</v>
       </c>
-      <c r="F7" t="n">
+      <c r="I7" t="n">
         <v>5029017.89</v>
       </c>
-      <c r="G7" t="n">
+      <c r="J7" t="n">
         <v>3279122.24</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="B8" t="n">
         <v>3623339.96</v>
       </c>
       <c r="C8" t="n">
+        <v>1471274.4532626</v>
+      </c>
+      <c r="D8" t="n">
+        <v>21413</v>
+      </c>
+      <c r="E8" t="n">
+        <v>443975.145376256</v>
+      </c>
+      <c r="F8" t="n">
         <v>1936662.59863886</v>
       </c>
-      <c r="D8" t="n">
+      <c r="G8" t="n">
         <v>645479.21</v>
       </c>
-      <c r="E8" t="n">
+      <c r="H8" t="n">
         <v>373255.01</v>
       </c>
-      <c r="F8" t="n">
+      <c r="I8" t="n">
         <v>1018734.22</v>
       </c>
-      <c r="G8" t="n">
+      <c r="J8" t="n">
         <v>290950</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="B9" t="n">
         <v>17824030.18</v>
       </c>
       <c r="C9" t="n">
+        <v>2015530.57486239</v>
+      </c>
+      <c r="D9" t="n">
+        <v>67451</v>
+      </c>
+      <c r="E9" t="n">
+        <v>635701.852423211</v>
+      </c>
+      <c r="F9" t="n">
         <v>2718683.4272856</v>
       </c>
-      <c r="D9" t="n">
+      <c r="G9" t="n">
         <v>1374452</v>
       </c>
-      <c r="E9" t="n">
+      <c r="H9" t="n">
         <v>576451.13</v>
       </c>
-      <c r="F9" t="n">
+      <c r="I9" t="n">
         <v>1950903.13</v>
       </c>
-      <c r="G9" t="n">
+      <c r="J9" t="n">
         <v>304572.59</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="B10" t="n">
         <v>21447370.14</v>
       </c>
       <c r="C10" t="n">
+        <v>3486805.02812498</v>
+      </c>
+      <c r="D10" t="n">
+        <v>88864</v>
+      </c>
+      <c r="E10" t="n">
+        <v>1079676.99779947</v>
+      </c>
+      <c r="F10" t="n">
         <v>4655346.02592445</v>
       </c>
-      <c r="D10" t="n">
+      <c r="G10" t="n">
         <v>2019931.21</v>
       </c>
-      <c r="E10" t="n">
+      <c r="H10" t="n">
         <v>949706.14</v>
       </c>
-      <c r="F10" t="n">
+      <c r="I10" t="n">
         <v>2969637.35</v>
       </c>
-      <c r="G10" t="n">
+      <c r="J10" t="n">
         <v>595522.59</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="B11" t="n">
         <v>4982999.91</v>
       </c>
       <c r="C11" t="n">
+        <v>2006329.99027918</v>
+      </c>
+      <c r="D11" t="n">
+        <v>15625</v>
+      </c>
+      <c r="E11" t="n">
+        <v>616642.204919514</v>
+      </c>
+      <c r="F11" t="n">
         <v>2638597.1951987</v>
       </c>
-      <c r="D11" t="n">
+      <c r="G11" t="n">
         <v>461056.58</v>
       </c>
-      <c r="E11" t="n">
+      <c r="H11" t="n">
         <v>57105.53</v>
       </c>
-      <c r="F11" t="n">
+      <c r="I11" t="n">
         <v>518162.11</v>
       </c>
-      <c r="G11" t="n">
+      <c r="J11" t="n">
         <v>26426.71</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="B12" t="n">
         <v>4959712.82</v>
       </c>
       <c r="C12" t="n">
+        <v>2723612.16972082</v>
+      </c>
+      <c r="D12" t="n">
+        <v>25174</v>
+      </c>
+      <c r="E12" t="n">
+        <v>838201.809250486</v>
+      </c>
+      <c r="F12" t="n">
         <v>3586987.97897131</v>
       </c>
-      <c r="D12" t="n">
+      <c r="G12" t="n">
         <v>1619513.17</v>
       </c>
-      <c r="E12" t="n">
+      <c r="H12" t="n">
         <v>163587.19</v>
       </c>
-      <c r="F12" t="n">
+      <c r="I12" t="n">
         <v>1783100.36</v>
       </c>
-      <c r="G12" t="n">
+      <c r="J12" t="n">
         <v>21219.18</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="B13" t="n">
         <v>9942712.73</v>
       </c>
       <c r="C13" t="n">
+        <v>4729942.16</v>
+      </c>
+      <c r="D13" t="n">
+        <v>40799</v>
+      </c>
+      <c r="E13" t="n">
+        <v>1454844.01417</v>
+      </c>
+      <c r="F13" t="n">
         <v>6225585.17417</v>
       </c>
-      <c r="D13" t="n">
+      <c r="G13" t="n">
         <v>2080569.75</v>
       </c>
-      <c r="E13" t="n">
+      <c r="H13" t="n">
         <v>220692.72</v>
       </c>
-      <c r="F13" t="n">
+      <c r="I13" t="n">
         <v>2301262.47</v>
       </c>
-      <c r="G13" t="n">
+      <c r="J13" t="n">
         <v>47645.89</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="B14" t="n">
         <v>16125916.84</v>
       </c>
       <c r="C14" t="n">
+        <v>2792170.83</v>
+      </c>
+      <c r="D14" t="n">
+        <v>62216</v>
+      </c>
+      <c r="E14" t="n">
+        <v>868183.739995</v>
+      </c>
+      <c r="F14" t="n">
         <v>3722570.569995</v>
       </c>
-      <c r="D14" t="n">
+      <c r="G14" t="n">
         <v>1369897.5</v>
       </c>
-      <c r="E14" t="n">
+      <c r="H14" t="n">
         <v>1152902.26</v>
       </c>
-      <c r="F14" t="n">
+      <c r="I14" t="n">
         <v>2522799.76</v>
       </c>
-      <c r="G14" t="n">
+      <c r="J14" t="n">
         <v>326408.8</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="B15" t="n">
         <v>184194167.17</v>
       </c>
       <c r="C15" t="n">
+        <v>21805472.2815888</v>
+      </c>
+      <c r="D15" t="n">
+        <v>660109</v>
+      </c>
+      <c r="E15" t="n">
+        <v>6839753.50980808</v>
+      </c>
+      <c r="F15" t="n">
         <v>29305334.7913969</v>
       </c>
-      <c r="D15" t="n">
+      <c r="G15" t="n">
         <v>19620684.1</v>
       </c>
-      <c r="E15" t="n">
+      <c r="H15" t="n">
         <v>5885242.55</v>
       </c>
-      <c r="F15" t="n">
+      <c r="I15" t="n">
         <v>25505926.65</v>
       </c>
-      <c r="G15" t="n">
+      <c r="J15" t="n">
         <v>6500762.63</v>
       </c>
     </row>
